--- a/Fischer_Tropsch/Memmingen_FischerTropsch_1_Naphta_Greenfield/Datenbank.xlsx
+++ b/Fischer_Tropsch/Memmingen_FischerTropsch_1_Naphta_Greenfield/Datenbank.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Fischer_Tropsch\Memmingen_1_FischerTropsch_Naphta_Greenfield\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Fischer_Tropsch\Memmingen_FischerTropsch_1_Naphta_Greenfield\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A771B4EA-8548-4882-A33B-1CF4476B81FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F303CC9-7B9E-4E3A-B693-232072CB8F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-4455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
     <sheet name="Ergebnisse" sheetId="5" r:id="rId2"/>
     <sheet name="Quelle" sheetId="6" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="9.8999999999999999E-4"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2413,7 +2413,7 @@
         <v>329</v>
       </c>
       <c r="E8" s="66">
-        <v>38.99</v>
+        <v>10</v>
       </c>
       <c r="F8" s="35" t="s">
         <v>340</v>
